--- a/Daily_Report/Top 7 broker List with its Turnover 2024-02-06.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-02-06.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="266">
   <si>
     <t>Date: 2024-02-06</t>
   </si>
@@ -59,12 +59,12 @@
     <t>7</t>
   </si>
   <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
@@ -80,12 +80,12 @@
     <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>58</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
@@ -101,67 +101,67 @@
     <t>57</t>
   </si>
   <si>
-    <t>297,669,553.5</t>
-  </si>
-  <si>
-    <t>239,822,286.31</t>
-  </si>
-  <si>
-    <t>216,973,391.3</t>
-  </si>
-  <si>
-    <t>175,769,590.7</t>
-  </si>
-  <si>
-    <t>142,729,896.1</t>
-  </si>
-  <si>
-    <t>139,963,641.6</t>
-  </si>
-  <si>
-    <t>111,917,957.3</t>
-  </si>
-  <si>
-    <t>133,646,328.9</t>
-  </si>
-  <si>
-    <t>123,714,527.43</t>
-  </si>
-  <si>
-    <t>98,364,647.3</t>
-  </si>
-  <si>
-    <t>95,726,175.3</t>
-  </si>
-  <si>
-    <t>75,631,637.59</t>
-  </si>
-  <si>
-    <t>49,048,140.0</t>
-  </si>
-  <si>
-    <t>55,927,826.3</t>
-  </si>
-  <si>
-    <t>164,023,224.6</t>
-  </si>
-  <si>
-    <t>116,107,758.88</t>
-  </si>
-  <si>
-    <t>118,608,744.0</t>
-  </si>
-  <si>
-    <t>80,043,415.4</t>
-  </si>
-  <si>
-    <t>67,098,258.5</t>
-  </si>
-  <si>
-    <t>90,915,501.6</t>
-  </si>
-  <si>
-    <t>55,990,131.0</t>
+    <t>328,000,396.31</t>
+  </si>
+  <si>
+    <t>298,470,889.2</t>
+  </si>
+  <si>
+    <t>267,238,978.8</t>
+  </si>
+  <si>
+    <t>169,974,614.0</t>
+  </si>
+  <si>
+    <t>143,771,244.5</t>
+  </si>
+  <si>
+    <t>139,051,623.8</t>
+  </si>
+  <si>
+    <t>127,458,248.9</t>
+  </si>
+  <si>
+    <t>182,622,594.63</t>
+  </si>
+  <si>
+    <t>150,845,519.3</t>
+  </si>
+  <si>
+    <t>103,570,249.8</t>
+  </si>
+  <si>
+    <t>85,094,247.4</t>
+  </si>
+  <si>
+    <t>73,200,151.9</t>
+  </si>
+  <si>
+    <t>56,253,578.7</t>
+  </si>
+  <si>
+    <t>60,541,181.2</t>
+  </si>
+  <si>
+    <t>145,377,801.68</t>
+  </si>
+  <si>
+    <t>147,625,369.9</t>
+  </si>
+  <si>
+    <t>163,668,729.0</t>
+  </si>
+  <si>
+    <t>84,880,366.59</t>
+  </si>
+  <si>
+    <t>70,571,092.59</t>
+  </si>
+  <si>
+    <t>82,798,045.09</t>
+  </si>
+  <si>
+    <t>66,917,067.7</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,286 +179,265 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>66,435,762.5</t>
+  </si>
+  <si>
+    <t>IGI</t>
+  </si>
+  <si>
+    <t>23,494,192.0</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>5,921,884.5</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>5,146,224.0</t>
+  </si>
+  <si>
+    <t>MBJC</t>
+  </si>
+  <si>
+    <t>4,818,705.0</t>
+  </si>
+  <si>
     <t>UNHPL</t>
   </si>
   <si>
-    <t>12,209,035.7</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>11,998,565.0</t>
+    <t>12,263,295.7</t>
+  </si>
+  <si>
+    <t>12,127,855.0</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>8,931,617.0</t>
+    <t>11,288,652.0</t>
+  </si>
+  <si>
+    <t>8,219,825.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>7,821,362.0</t>
+  </si>
+  <si>
+    <t>16,962,893.0</t>
+  </si>
+  <si>
+    <t>8,755,911.0</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>6,559,573.2</t>
+  </si>
+  <si>
+    <t>4,571,934.0</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>2,905,837.2</t>
+  </si>
+  <si>
+    <t>KPCL</t>
+  </si>
+  <si>
+    <t>8,385,776.5</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>7,872,585.8</t>
+  </si>
+  <si>
+    <t>4,504,900.3</t>
+  </si>
+  <si>
+    <t>4,273,314.0</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>3,715,221.6</t>
+  </si>
+  <si>
+    <t>11,663,635.0</t>
+  </si>
+  <si>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>3,547,182.0</t>
+  </si>
+  <si>
+    <t>2,392,744.0</t>
+  </si>
+  <si>
+    <t>2,377,020.0</t>
+  </si>
+  <si>
+    <t>USHEC</t>
+  </si>
+  <si>
+    <t>2,346,112.0</t>
+  </si>
+  <si>
+    <t>4,951,368.0</t>
+  </si>
+  <si>
+    <t>2,396,587.5</t>
+  </si>
+  <si>
+    <t>2,275,030.2</t>
+  </si>
+  <si>
+    <t>2,153,111.0</t>
   </si>
   <si>
     <t>UMHL</t>
   </si>
   <si>
-    <t>5,100,342.7</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>4,953,085.0</t>
-  </si>
-  <si>
-    <t>IGI</t>
-  </si>
-  <si>
-    <t>23,308,602.0</t>
-  </si>
-  <si>
-    <t>RAWA</t>
-  </si>
-  <si>
-    <t>9,795,294.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>4,818,705.0</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>3,824,642.2</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>3,700,764.5</t>
-  </si>
-  <si>
-    <t>15,505,628.0</t>
-  </si>
-  <si>
-    <t>8,259,191.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>6,335,820.0</t>
-  </si>
-  <si>
-    <t>4,260,434.0</t>
-  </si>
-  <si>
-    <t>3,968,753.5</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>24,151,374.0</t>
-  </si>
-  <si>
-    <t>KPCL</t>
-  </si>
-  <si>
-    <t>8,385,776.5</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>3,727,335.8</t>
-  </si>
-  <si>
-    <t>3,527,755.3</t>
-  </si>
-  <si>
-    <t>3,393,006.0</t>
-  </si>
-  <si>
-    <t>17,594,073.0</t>
-  </si>
-  <si>
-    <t>5,153,002.5</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>3,269,399.0</t>
-  </si>
-  <si>
-    <t>USHEC</t>
-  </si>
-  <si>
-    <t>2,310,783.0</t>
-  </si>
-  <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>2,194,861.0</t>
-  </si>
-  <si>
-    <t>4,944,448.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>3,566,705.0</t>
-  </si>
-  <si>
-    <t>2,752,116.0</t>
-  </si>
-  <si>
-    <t>2,228,170.2</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>1,413,678.0</t>
-  </si>
-  <si>
-    <t>7,898,498.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>3,520,171.0</t>
-  </si>
-  <si>
-    <t>2,483,469.0</t>
+    <t>1,967,825.0</t>
+  </si>
+  <si>
+    <t>6,760,928.0</t>
+  </si>
+  <si>
+    <t>2,942,387.5</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>2,455,786.0</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>1,812,820.0</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>1,516,279.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>43,331,206.0</t>
+  </si>
+  <si>
+    <t>12,068,704.0</t>
+  </si>
+  <si>
+    <t>7,261,093.8</t>
+  </si>
+  <si>
+    <t>6,786,211.5</t>
+  </si>
+  <si>
+    <t>SKBBL</t>
+  </si>
+  <si>
+    <t>6,406,795.2</t>
+  </si>
+  <si>
+    <t>28,348,628.8</t>
+  </si>
+  <si>
+    <t>20,157,653.89</t>
+  </si>
+  <si>
+    <t>8,459,826.1</t>
+  </si>
+  <si>
+    <t>6,058,365.0</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>3,230,569.0</t>
+  </si>
+  <si>
+    <t>36,703,344.0</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>17,372,682.2</t>
+  </si>
+  <si>
+    <t>11,912,752.8</t>
+  </si>
+  <si>
+    <t>8,232,842.7</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>7,477,728.8</t>
+  </si>
+  <si>
+    <t>11,854,016.3</t>
+  </si>
+  <si>
+    <t>8,568,193.0</t>
+  </si>
+  <si>
+    <t>4,494,536.9</t>
+  </si>
+  <si>
+    <t>3,810,337.0</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>3,337,690.0</t>
+  </si>
+  <si>
+    <t>11,509,587.0</t>
   </si>
   <si>
     <t>API</t>
   </si>
   <si>
-    <t>1,972,575.8</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>1,836,336.9</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>28,032,213.9</t>
-  </si>
-  <si>
-    <t>27,015,442.8</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>23,595,145.0</t>
-  </si>
-  <si>
-    <t>7,525,857.1</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>3,804,358.0</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>14,479,339.2</t>
-  </si>
-  <si>
-    <t>10,877,329.5</t>
-  </si>
-  <si>
-    <t>7,826,093.0</t>
-  </si>
-  <si>
-    <t>7,261,093.8</t>
-  </si>
-  <si>
-    <t>SKBBL</t>
-  </si>
-  <si>
-    <t>6,406,795.2</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>15,953,303.8</t>
-  </si>
-  <si>
-    <t>10,314,939.8</t>
-  </si>
-  <si>
-    <t>6,898,980.7</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>6,582,547.8</t>
-  </si>
-  <si>
-    <t>6,208,435.6</t>
-  </si>
-  <si>
-    <t>12,505,715.3</t>
-  </si>
-  <si>
-    <t>8,568,193.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>4,398,212.9</t>
-  </si>
-  <si>
-    <t>3,508,055.0</t>
-  </si>
-  <si>
-    <t>3,377,342.0</t>
-  </si>
-  <si>
-    <t>11,060,046.0</t>
-  </si>
-  <si>
-    <t>10,803,970.4</t>
-  </si>
-  <si>
-    <t>4,398,496.5</t>
-  </si>
-  <si>
-    <t>3,065,171.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>2,142,239.0</t>
-  </si>
-  <si>
-    <t>19,666,625.0</t>
-  </si>
-  <si>
-    <t>HLBSL</t>
-  </si>
-  <si>
-    <t>7,660,370.0</t>
+    <t>4,997,218.59</t>
+  </si>
+  <si>
+    <t>3,766,991.0</t>
+  </si>
+  <si>
+    <t>2,520,490.4</t>
+  </si>
+  <si>
+    <t>2,152,474.0</t>
+  </si>
+  <si>
+    <t>11,724,989.0</t>
   </si>
   <si>
     <t>SPC</t>
@@ -467,19 +446,22 @@
     <t>6,634,928.5</t>
   </si>
   <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>5,119,505.0</t>
-  </si>
-  <si>
-    <t>4,051,312.5</t>
-  </si>
-  <si>
-    <t>7,065,770.0</t>
-  </si>
-  <si>
-    <t>3,466,908.2</t>
+    <t>4,133,488.5</t>
+  </si>
+  <si>
+    <t>3,857,648.5</t>
+  </si>
+  <si>
+    <t>2,293,172.5</t>
+  </si>
+  <si>
+    <t>7,568,881.0</t>
+  </si>
+  <si>
+    <t>4,376,754.7</t>
+  </si>
+  <si>
+    <t>3,162,261.1</t>
   </si>
   <si>
     <t>PRIN</t>
@@ -491,10 +473,7 @@
     <t>HURJA</t>
   </si>
   <si>
-    <t>2,556,925.0</t>
-  </si>
-  <si>
-    <t>2,032,991.4</t>
+    <t>2,861,925.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -512,109 +491,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>321,932,296.5</t>
-  </si>
-  <si>
-    <t>105,933,653.2</t>
-  </si>
-  <si>
-    <t>74,851,309.8</t>
-  </si>
-  <si>
-    <t>52,656,286.4</t>
-  </si>
-  <si>
-    <t>50,220,243.7</t>
+    <t>337,602,470.0</t>
+  </si>
+  <si>
+    <t>166,554,725.69</t>
+  </si>
+  <si>
+    <t>87,461,214.6</t>
+  </si>
+  <si>
+    <t>73,593,735.2</t>
+  </si>
+  <si>
+    <t>73,056,841.7</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>844,439,322.8</t>
+    <t>894,626,420.3</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>689,968,769.1</t>
+    <t>757,238,083.5</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>161,054,949.8</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>173,077,911.1</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>116,928,807.1</t>
+    <t>160,040,870.9</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>104,600,851.2</t>
+    <t>103,923,776.6</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>101,486,718.8</t>
+    <t>96,408,777.4</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>92,660,517.2</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>87,876,928.6</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>75,109,746.3</t>
+    <t>91,048,039.1</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>72,118,140.09</t>
+    <t>72,984,868.3</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>67,928,019.0</t>
+    <t>64,746,579.5</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>57,681,930.7</t>
+    <t>42,499,335.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>34,203,143.29</t>
+    <t>38,615,946.7</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>25,554,878.81</t>
+    <t>13,179,312.56</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>1,461,715.0</t>
+    <t>1,620,565.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>812,865.0</t>
+    <t>886,865.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -626,214 +605,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>45,805,844.0</t>
-  </si>
-  <si>
-    <t>41,881,272.79</t>
-  </si>
-  <si>
-    <t>8,864,058.6</t>
-  </si>
-  <si>
-    <t>8,790,423.6</t>
-  </si>
-  <si>
-    <t>6,294,844.3</t>
-  </si>
-  <si>
-    <t>36,979,753.79</t>
-  </si>
-  <si>
-    <t>28,772,404.9</t>
-  </si>
-  <si>
-    <t>23,866,095.6</t>
-  </si>
-  <si>
-    <t>10,461,344.0</t>
-  </si>
-  <si>
-    <t>5,236,191.7</t>
-  </si>
-  <si>
-    <t>38,752,417.79</t>
-  </si>
-  <si>
-    <t>25,482,206.4</t>
-  </si>
-  <si>
-    <t>8,295,792.5</t>
-  </si>
-  <si>
-    <t>7,238,559.5</t>
-  </si>
-  <si>
-    <t>2,857,652.0</t>
-  </si>
-  <si>
-    <t>24,576,539.0</t>
-  </si>
-  <si>
-    <t>23,220,342.6</t>
-  </si>
-  <si>
-    <t>15,279,812.3</t>
-  </si>
-  <si>
-    <t>7,679,083.0</t>
-  </si>
-  <si>
-    <t>5,965,313.8</t>
-  </si>
-  <si>
-    <t>32,291,342.7</t>
-  </si>
-  <si>
-    <t>18,350,790.3</t>
-  </si>
-  <si>
-    <t>7,555,846.1</t>
-  </si>
-  <si>
-    <t>4,262,209.9</t>
-  </si>
-  <si>
-    <t>2,820,944.5</t>
-  </si>
-  <si>
-    <t>23,971,270.3</t>
-  </si>
-  <si>
-    <t>12,926,933.5</t>
-  </si>
-  <si>
-    <t>2,790,154.4</t>
-  </si>
-  <si>
-    <t>2,153,419.0</t>
-  </si>
-  <si>
-    <t>1,707,574.2</t>
-  </si>
-  <si>
-    <t>24,868,949.0</t>
-  </si>
-  <si>
-    <t>13,050,840.5</t>
-  </si>
-  <si>
-    <t>4,450,052.3</t>
-  </si>
-  <si>
-    <t>3,032,215.4</t>
-  </si>
-  <si>
-    <t>2,545,366.6</t>
-  </si>
-  <si>
-    <t>81,882,716.0</t>
-  </si>
-  <si>
-    <t>54,685,713.0</t>
-  </si>
-  <si>
-    <t>5,565,180.7</t>
-  </si>
-  <si>
-    <t>4,415,982.7</t>
-  </si>
-  <si>
-    <t>3,717,553.7</t>
-  </si>
-  <si>
-    <t>38,723,562.9</t>
-  </si>
-  <si>
-    <t>31,026,967.6</t>
-  </si>
-  <si>
-    <t>10,575,883.0</t>
-  </si>
-  <si>
-    <t>8,474,888.19</t>
-  </si>
-  <si>
-    <t>6,109,360.0</t>
-  </si>
-  <si>
-    <t>39,966,260.6</t>
-  </si>
-  <si>
-    <t>26,466,394.3</t>
-  </si>
-  <si>
-    <t>16,322,864.8</t>
-  </si>
-  <si>
-    <t>10,661,198.3</t>
-  </si>
-  <si>
-    <t>5,975,756.7</t>
-  </si>
-  <si>
-    <t>27,777,438.6</t>
-  </si>
-  <si>
-    <t>23,736,696.1</t>
-  </si>
-  <si>
-    <t>7,906,267.9</t>
-  </si>
-  <si>
-    <t>6,451,048.5</t>
-  </si>
-  <si>
-    <t>3,628,488.0</t>
-  </si>
-  <si>
-    <t>21,921,716.3</t>
-  </si>
-  <si>
-    <t>17,155,435.1</t>
-  </si>
-  <si>
-    <t>12,007,289.0</t>
-  </si>
-  <si>
-    <t>4,229,124.4</t>
-  </si>
-  <si>
-    <t>2,495,989.6</t>
-  </si>
-  <si>
-    <t>42,847,778.29</t>
-  </si>
-  <si>
-    <t>29,590,504.3</t>
-  </si>
-  <si>
-    <t>3,755,523.9</t>
-  </si>
-  <si>
-    <t>3,045,216.6</t>
-  </si>
-  <si>
-    <t>2,924,227.3</t>
-  </si>
-  <si>
-    <t>20,743,902.3</t>
-  </si>
-  <si>
-    <t>17,396,885.8</t>
-  </si>
-  <si>
-    <t>3,914,857.5</t>
-  </si>
-  <si>
-    <t>2,600,112.9</t>
-  </si>
-  <si>
-    <t>2,598,506.6</t>
+    <t>93,515,905.4</t>
+  </si>
+  <si>
+    <t>30,449,840.8</t>
+  </si>
+  <si>
+    <t>24,051,685.6</t>
+  </si>
+  <si>
+    <t>9,388,515.0</t>
+  </si>
+  <si>
+    <t>5,092,886.7</t>
+  </si>
+  <si>
+    <t>48,500,907.5</t>
+  </si>
+  <si>
+    <t>47,075,350.4</t>
+  </si>
+  <si>
+    <t>15,324,497.5</t>
+  </si>
+  <si>
+    <t>8,775,067.8</t>
+  </si>
+  <si>
+    <t>7,570,368.7</t>
+  </si>
+  <si>
+    <t>42,490,554.29</t>
+  </si>
+  <si>
+    <t>25,956,044.7</t>
+  </si>
+  <si>
+    <t>7,148,602.7</t>
+  </si>
+  <si>
+    <t>6,530,477.0</t>
+  </si>
+  <si>
+    <t>3,058,266.7</t>
+  </si>
+  <si>
+    <t>24,317,192.1</t>
+  </si>
+  <si>
+    <t>17,946,279.3</t>
+  </si>
+  <si>
+    <t>11,200,984.3</t>
+  </si>
+  <si>
+    <t>8,220,121.9</t>
+  </si>
+  <si>
+    <t>5,264,864.2</t>
+  </si>
+  <si>
+    <t>29,128,502.3</t>
+  </si>
+  <si>
+    <t>18,748,420.1</t>
+  </si>
+  <si>
+    <t>4,645,386.7</t>
+  </si>
+  <si>
+    <t>4,444,431.9</t>
+  </si>
+  <si>
+    <t>3,222,009.0</t>
+  </si>
+  <si>
+    <t>21,933,365.8</t>
+  </si>
+  <si>
+    <t>19,002,649.0</t>
+  </si>
+  <si>
+    <t>3,437,515.4</t>
+  </si>
+  <si>
+    <t>2,547,711.29</t>
+  </si>
+  <si>
+    <t>2,183,684.0</t>
+  </si>
+  <si>
+    <t>26,250,479.9</t>
+  </si>
+  <si>
+    <t>14,610,254.6</t>
+  </si>
+  <si>
+    <t>3,998,658.9</t>
+  </si>
+  <si>
+    <t>3,347,595.1</t>
+  </si>
+  <si>
+    <t>2,525,788.4</t>
+  </si>
+  <si>
+    <t>59,322,585.2</t>
+  </si>
+  <si>
+    <t>37,071,614.1</t>
+  </si>
+  <si>
+    <t>10,993,392.2</t>
+  </si>
+  <si>
+    <t>8,925,712.19</t>
+  </si>
+  <si>
+    <t>6,605,030.5</t>
+  </si>
+  <si>
+    <t>57,921,682.7</t>
+  </si>
+  <si>
+    <t>57,834,864.9</t>
+  </si>
+  <si>
+    <t>7,147,708.8</t>
+  </si>
+  <si>
+    <t>5,151,472.2</t>
+  </si>
+  <si>
+    <t>3,911,094.9</t>
+  </si>
+  <si>
+    <t>61,880,572.8</t>
+  </si>
+  <si>
+    <t>43,494,874.2</t>
+  </si>
+  <si>
+    <t>17,788,703.2</t>
+  </si>
+  <si>
+    <t>11,912,172.7</t>
+  </si>
+  <si>
+    <t>6,353,971.7</t>
+  </si>
+  <si>
+    <t>29,724,111.5</t>
+  </si>
+  <si>
+    <t>25,566,731.6</t>
+  </si>
+  <si>
+    <t>7,187,782.5</t>
+  </si>
+  <si>
+    <t>6,935,383.1</t>
+  </si>
+  <si>
+    <t>4,489,352.2</t>
+  </si>
+  <si>
+    <t>24,723,644.0</t>
+  </si>
+  <si>
+    <t>21,768,934.5</t>
+  </si>
+  <si>
+    <t>4,885,257.8</t>
+  </si>
+  <si>
+    <t>4,462,373.8</t>
+  </si>
+  <si>
+    <t>2,877,455.7</t>
+  </si>
+  <si>
+    <t>30,095,955.5</t>
+  </si>
+  <si>
+    <t>28,828,146.1</t>
+  </si>
+  <si>
+    <t>5,177,061.5</t>
+  </si>
+  <si>
+    <t>4,388,224.7</t>
+  </si>
+  <si>
+    <t>3,537,870.3</t>
+  </si>
+  <si>
+    <t>24,199,838.3</t>
+  </si>
+  <si>
+    <t>20,714,085.8</t>
+  </si>
+  <si>
+    <t>4,951,680.09</t>
+  </si>
+  <si>
+    <t>4,185,463.5</t>
+  </si>
+  <si>
+    <t>2,526,026.7</t>
   </si>
 </sst>
 </file>
@@ -1642,7 +1621,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04101539964852334</v>
+        <v>0.2025478116715755</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1651,52 +1630,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.09719114248569354</v>
+        <v>0.04108707463186664</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J9" s="14">
-        <v>0.07146326979127601</v>
+        <v>0.06347462139007395</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.1374035969692908</v>
+        <v>0.04933546429468579</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1232683094484506</v>
+        <v>0.08112634094921534</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S9" s="16">
-        <v>0.03532666014885969</v>
+        <v>0.03560812786423569</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="V9" s="18">
-        <v>0.07057400072829957</v>
+        <v>0.0530442561258191</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1708,61 +1687,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04030833808470103</v>
+        <v>0.0716285476002753</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.0408439688851034</v>
+        <v>0.04063329268896753</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03806545563266955</v>
+        <v>0.03276434837207214</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.04770891521453603</v>
+        <v>0.04631624461285731</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>89</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03610317558410946</v>
+        <v>0.02467240241493493</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0254830823150003</v>
+        <v>0.01723523562333257</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03145313839640639</v>
+        <v>0.02308510846017123</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1774,61 +1753,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03000514125473031</v>
+        <v>0.01805450410005939</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.02009281570175353</v>
+        <v>0.03782161814928515</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02920090782578831</v>
+        <v>0.02454572019940678</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="L11" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.02650337126225214</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M11" s="16">
-        <v>0.02120580576626444</v>
-      </c>
-      <c r="N11" s="17" t="s">
+      <c r="O11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.02290619617427158</v>
+        <v>0.01664271606134702</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01966307798610464</v>
+        <v>0.01636104734218861</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02219008512943972</v>
+        <v>0.01926737595404074</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1840,61 +1819,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01713424379494022</v>
+        <v>0.01568968835981587</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01594781810667995</v>
+        <v>0.02753978795731747</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0196357441549562</v>
+        <v>0.01710803573838533</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02007033916362189</v>
+        <v>0.02514089545159962</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01618990178750645</v>
+        <v>0.01653334787680717</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>54</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01591963580347427</v>
+        <v>0.01548425643052433</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01762519480866186</v>
+        <v>0.01422285348845711</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1906,61 +1885,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01663954187373752</v>
+        <v>0.01469115602971937</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01543127853937771</v>
+        <v>0.02620477333975121</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01829142954452222</v>
+        <v>0.01087355300131838</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01930371451903256</v>
+        <v>0.0218575086747954</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01537772435889835</v>
+        <v>0.01631836747438046</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01010032308276266</v>
+        <v>0.01415175850682874</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01640788434940458</v>
+        <v>0.01189627986486483</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1971,7 +1950,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1980,7 +1959,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1989,7 +1968,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1998,7 +1977,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2007,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2016,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2025,7 +2004,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2034,566 +2013,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D16" s="10">
-        <v>0.09417225769447059</v>
+        <v>0.1321071757457475</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12">
-        <v>0.06037528631214725</v>
+        <v>0.09497954348574372</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J16" s="14">
-        <v>0.07352654491140823</v>
+        <v>0.1373427789793664</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="M16" s="16">
-        <v>0.07114834397802351</v>
+        <v>0.06973992186856798</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="P16" s="18">
-        <v>0.07748934387404771</v>
+        <v>0.08005486104003225</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="S16" s="16">
-        <v>0.140512384324816</v>
+        <v>0.08432112246933716</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="V16" s="18">
-        <v>0.06313347893814714</v>
+        <v>0.05938321815434889</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09075648645403031</v>
+        <v>0.03679478481054522</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G17" s="12">
-        <v>0.04535579102077154</v>
+        <v>0.06753641520628403</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J17" s="14">
-        <v>0.04754011419648212</v>
+        <v>0.06500803991247701</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="M17" s="16">
-        <v>0.04874673125127782</v>
+        <v>0.05040866279007993</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>135</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P17" s="18">
-        <v>0.07569521659590139</v>
+        <v>0.03475812299865012</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="R17" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.04771557727037488</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="S17" s="16">
-        <v>0.05473114240548597</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>154</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.03097722906706411</v>
+        <v>0.03433873239097984</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D18" s="10">
-        <v>0.07926623573881902</v>
+        <v>0.02213745434971179</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03263288462642628</v>
+        <v>0.02834389016186842</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J18" s="14">
-        <v>0.0317964366905298</v>
+        <v>0.04457715282962307</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02502260420863573</v>
+        <v>0.02644240098112534</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03081692497637851</v>
+        <v>0.02620128255201964</v>
       </c>
       <c r="Q18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.02972628716616253</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="R18" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.04740465755357998</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>156</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.0274678083317734</v>
+        <v>0.02481017217238735</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.02068964420880215</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.02029800968609839</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0.02528258940664551</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.03027697680529214</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="I19" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.03080704295821085</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.03033804173203242</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="M19" s="16">
-        <v>0.01995825891173336</v>
+        <v>0.02241709459037218</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02147532565884072</v>
+        <v>0.01753125535475211</v>
       </c>
       <c r="Q19" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.02774256347806849</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="R19" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.03657739211038076</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>158</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.02284642305565025</v>
+        <v>0.0241188077392455</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0127804740366233</v>
+        <v>0.0195328885942711</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02671476157857333</v>
+        <v>0.01082373228645174</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="I20" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.02798143008021403</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.02861381095074398</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>80</v>
-      </c>
       <c r="L20" s="15" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01921459785250556</v>
+        <v>0.01963640288072665</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01500904196342367</v>
+        <v>0.01497151956558323</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="R20" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.01649151902963969</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="S20" s="16">
-        <v>0.02894546364818219</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01816501524014145</v>
+        <v>0.02245382330841044</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3258452434005195</v>
+        <v>0.3452110244091879</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2662394270800605</v>
+        <v>0.2921967522924554</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D33" s="22">
-        <v>0.06678586909315465</v>
+        <v>0.06214654848666818</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D34" s="22">
-        <v>0.04511951845598241</v>
+        <v>0.06175524412994758</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D35" s="22">
-        <v>0.04036250906240426</v>
+        <v>0.04010124513037209</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D36" s="22">
-        <v>0.03916085347571888</v>
+        <v>0.03720141955692628</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03390922049201978</v>
+        <v>0.03575507199325799</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02898272605747815</v>
+        <v>0.0351328623154444</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D39" s="22">
-        <v>0.02782834986480483</v>
+        <v>0.0281627957553096</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02621150068115955</v>
+        <v>0.02498387318886778</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D41" s="22">
-        <v>0.02225782509326009</v>
+        <v>0.0163992913129364</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01319802530831567</v>
+        <v>0.01490080129130029</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="D43" s="22">
-        <v>0.009860904722324742</v>
+        <v>0.005085523841695644</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0005640344629829575</v>
+        <v>0.0006253301837252656</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D45" s="22">
-        <v>0.000313661605547348</v>
+        <v>0.0003422161119051119</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2972,331 +2951,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1538815221826172</v>
+        <v>0.2851091231963518</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1541964859437587</v>
+        <v>0.1624979495655283</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1786044711188509</v>
+        <v>0.1589983410758341</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1398224738541193</v>
+        <v>0.1430636700842868</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2262409178619167</v>
+        <v>0.2026031172040109</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="S9" s="16">
-        <v>0.171267838032588</v>
+        <v>0.1577354165352796</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="V9" s="18">
-        <v>0.2222069594545754</v>
+        <v>0.2059535583341911</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1406972003268719</v>
+        <v>0.09283476831906393</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G10" s="12">
-        <v>0.119973857904132</v>
+        <v>0.1577217480946882</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1174439236411566</v>
+        <v>0.09712671712993388</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="M10" s="16">
-        <v>0.132106711448353</v>
+        <v>0.1055821153387058</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1285700529561305</v>
+        <v>0.1304045197995069</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09235922524039272</v>
+        <v>0.1366589506882119</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1166107818159758</v>
+        <v>0.1146277681208595</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02977818354539911</v>
+        <v>0.0733282211563801</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G11" s="12">
-        <v>0.09951575379925333</v>
+        <v>0.05134335727371833</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J11" s="14">
-        <v>0.03823414682462033</v>
+        <v>0.02674985038522382</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M11" s="16">
-        <v>0.08693092041204828</v>
+        <v>0.06589798344828128</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05293807608958247</v>
+        <v>0.03231095839891683</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01993485142358571</v>
+        <v>0.02472114532761033</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="V11" s="18">
-        <v>0.03976173625177485</v>
+        <v>0.03137230375051858</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02953081192430384</v>
+        <v>0.02862348675678647</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04362123371002067</v>
+        <v>0.02940007926240332</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0333615078633838</v>
+        <v>0.02443684311818662</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04368834773647795</v>
+        <v>0.04836087993704755</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="P12" s="18">
-        <v>0.02986206825943314</v>
+        <v>0.03091321853307043</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01538555995959454</v>
+        <v>0.01832205356813675</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02709319820654018</v>
+        <v>0.02626424832359359</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02114708819220908</v>
+        <v>0.01552707483678345</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02183363264759962</v>
+        <v>0.02536384275294342</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01317051820445966</v>
+        <v>0.01144393947968492</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03393825846805024</v>
+        <v>0.03097441480290698</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01976421602677815</v>
+        <v>0.02241066362891503</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01220012697926259</v>
+        <v>0.01570412441310879</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02274314740374555</v>
+        <v>0.01981659423221528</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3307,7 +3286,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3316,7 +3295,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3325,7 +3304,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3334,7 +3313,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3343,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3352,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3361,7 +3340,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3370,331 +3349,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2750792448781632</v>
+        <v>0.1808613217160049</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1614677413672264</v>
+        <v>0.1940614136783963</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1841989027343004</v>
+        <v>0.2315551910797827</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1580332439153823</v>
+        <v>0.1748738285118271</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1535888198548195</v>
+        <v>0.1719651526004562</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="S16" s="16">
-        <v>0.3061350634363603</v>
+        <v>0.2164372819068079</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="V16" s="18">
-        <v>0.185349186139944</v>
+        <v>0.1898648263949278</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D17" s="10">
-        <v>0.183712819658595</v>
+        <v>0.1130230771580009</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1293748303270439</v>
+        <v>0.1937705384100152</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1219799079574971</v>
+        <v>0.1627564751044469</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="M17" s="16">
-        <v>0.135044383988544</v>
+        <v>0.1504150002070309</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1201951067629202</v>
+        <v>0.1514136889870213</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="S17" s="16">
-        <v>0.2114156502484142</v>
+        <v>0.2073197371751943</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1554432033937775</v>
+        <v>0.1625166356730011</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01869583447337687</v>
+        <v>0.03351639913754834</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04409883319321442</v>
+        <v>0.02394775858764051</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07522979984873381</v>
+        <v>0.06656477763789448</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0449808631203691</v>
+        <v>0.04228738828022872</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08412595628590247</v>
+        <v>0.03397938034820308</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02683213909747258</v>
+        <v>0.03723121930202155</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03497970830101989</v>
+        <v>0.03884942828521787</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01483518434477714</v>
+        <v>0.02721250431528175</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03533820117553695</v>
+        <v>0.01725954653000712</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0491359711719637</v>
+        <v>0.04457498211335029</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03670173250281114</v>
+        <v>0.0408024641844458</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02963026328441362</v>
+        <v>0.03103801330731334</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0217571975492241</v>
+        <v>0.03155824132130703</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02323231197858898</v>
+        <v>0.03283791779756673</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01248886107527285</v>
+        <v>0.02013726377866156</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02547452988627961</v>
+        <v>0.01310377340478</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02754142645877518</v>
+        <v>0.02377636574025106</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02064343431391969</v>
+        <v>0.02641189819086749</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01748750379704088</v>
+        <v>0.02001412528636768</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02089276376758691</v>
+        <v>0.02544285498663842</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02321795950076726</v>
+        <v>0.01981846386405204</v>
       </c>
     </row>
   </sheetData>
